--- a/artfynd/A 58412-2025 artfynd.xlsx
+++ b/artfynd/A 58412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130313697</v>
       </c>
       <c r="B2" t="n">
-        <v>97783</v>
+        <v>97786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58412-2025 artfynd.xlsx
+++ b/artfynd/A 58412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130313697</v>
       </c>
       <c r="B2" t="n">
-        <v>97786</v>
+        <v>97812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58412-2025 artfynd.xlsx
+++ b/artfynd/A 58412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130313697</v>
       </c>
       <c r="B2" t="n">
-        <v>97812</v>
+        <v>97813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58412-2025 artfynd.xlsx
+++ b/artfynd/A 58412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130313697</v>
       </c>
       <c r="B2" t="n">
-        <v>97813</v>
+        <v>97814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58412-2025 artfynd.xlsx
+++ b/artfynd/A 58412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130313697</v>
       </c>
       <c r="B2" t="n">
-        <v>97814</v>
+        <v>97816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58412-2025 artfynd.xlsx
+++ b/artfynd/A 58412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130313697</v>
       </c>
       <c r="B2" t="n">
-        <v>97816</v>
+        <v>97820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58412-2025 artfynd.xlsx
+++ b/artfynd/A 58412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130313697</v>
       </c>
       <c r="B2" t="n">
-        <v>97820</v>
+        <v>97833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58412-2025 artfynd.xlsx
+++ b/artfynd/A 58412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130313697</v>
       </c>
       <c r="B2" t="n">
-        <v>97833</v>
+        <v>97834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58412-2025 artfynd.xlsx
+++ b/artfynd/A 58412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130313697</v>
       </c>
       <c r="B2" t="n">
-        <v>97834</v>
+        <v>97837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
